--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaylozano/Documents/Codex/2026-09-02/bus/outputs/final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBE04EF-37F4-6042-9A8C-B29B30186910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE39AC62-2468-2E41-9788-8463CD32A270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1660" yWindow="1060" windowWidth="44800" windowHeight="23260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22320" yWindow="600" windowWidth="22480" windowHeight="23240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -127,6 +127,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -903,11 +925,11 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1174,7 +1196,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21"/>
@@ -1182,7 +1204,7 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="21"/>
@@ -1546,7 +1568,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="21"/>
@@ -1554,7 +1576,7 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="21"/>
@@ -1826,7 +1848,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="21"/>
@@ -1853,7 +1875,7 @@
       <c r="W1" s="21"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B2" s="21"/>
@@ -4228,7 +4250,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>90</v>
       </c>
       <c r="B1" s="21"/>
@@ -4237,7 +4259,7 @@
       <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>91</v>
       </c>
       <c r="B2" s="21"/>
@@ -4606,7 +4628,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="21"/>
@@ -4617,7 +4639,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B2" s="21"/>
@@ -5066,8 +5088,8 @@
       <c r="A22" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="18">
-        <f>0</f>
+      <c r="B22" s="18" cm="1">
+        <f t="array" ref="B22">SUMPRODUCT(--ISERROR('Cost Structure'!B4:B18))+SUMPRODUCT(--ISERROR('Marginal-Cost Schedules'!B5:W35))+SUMPRODUCT(--ISERROR(Optimization!B10:B28))</f>
         <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
